--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128410730</v>
+        <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagalund, Hagalund, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642396</v>
+        <v>642513</v>
       </c>
       <c r="R2" t="n">
-        <v>6619589</v>
+        <v>6619517</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Några år gamla gnagspår i gran som dödats ab blixtnedslag</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,35 +782,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128409598</v>
+        <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>92682</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagalund, Hagalund, Upl</t>
@@ -862,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,122 +895,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>128409622</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57833</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Hagalund, Hagalund, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>642513</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6619517</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Håbo</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Häggeby</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,6 +895,128 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128410730</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hagalund, Hagalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>642396</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619589</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Några år gamla gnagspår i gran som dödats av blixtnedslag</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128409622</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>128409598</v>
       </c>
       <c r="B2" t="n">
-        <v>92841</v>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -782,57 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128409622</v>
+        <v>2008064</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6431</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Upl</t>
+          <t>SV FATTASBO (11H4j04), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642513</v>
+        <v>641883</v>
       </c>
       <c r="R3" t="n">
-        <v>6619517</v>
+        <v>6619868</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>1996-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>1996-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>110749041 / BAC RUBE / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +872,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Roine Schenning</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>128410730</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,6 +1008,227 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128409622</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagalund, Hagalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>642513</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619517</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>65113735</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fattasbo 4 km NNV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>641900</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619874</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2009-02-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2009-02-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Levande ask (2-3 ihopväxta träd), omkr. 515 cm.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4521-2024 artfynd.xlsx
+++ b/artfynd/A 4521-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2008064</t>
         </is>
       </c>
     </row>
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,8 +1253,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65113735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>